--- a/examples/purchase_process.xlsx
+++ b/examples/purchase_process.xlsx
@@ -59,12 +59,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FC"/>
+        <fgColor rgb="00D4DFF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4DFF0"/>
+        <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,6 +82,20 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="00333333"/>
+      </left>
+      <right style="medium">
+        <color rgb="00333333"/>
+      </right>
+      <top style="medium">
+        <color rgb="00333333"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="008A99B3"/>
       </left>
@@ -93,20 +107,6 @@
       </top>
       <bottom style="thin">
         <color rgb="008A99B3"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00333333"/>
-      </left>
-      <right style="medium">
-        <color rgb="00333333"/>
-      </right>
-      <top style="medium">
-        <color rgb="00333333"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00333333"/>
       </bottom>
     </border>
   </borders>
@@ -121,11 +121,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -207,15 +207,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -224,7 +224,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="847725" y="1393825"/>
+          <a:off x="1047750" y="1114425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -259,16 +259,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -277,7 +277,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="847725" y="2282825"/>
+          <a:off x="2514600" y="1114425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -312,16 +312,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -330,7 +330,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2447925" y="3171825"/>
+          <a:off x="3981450" y="2257425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -365,16 +365,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -383,7 +383,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="847725" y="4060825"/>
+          <a:off x="5448300" y="1114425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -418,16 +418,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -436,7 +436,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="4060825"/>
+          <a:off x="5448300" y="3400425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -471,16 +471,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -489,7 +489,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="4949825"/>
+          <a:off x="6915150" y="3400425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -524,16 +524,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -542,7 +542,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="5838825"/>
+          <a:off x="8382000" y="3400425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -577,16 +577,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -595,7 +595,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="8505825"/>
+          <a:off x="9848850" y="3686175"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -630,16 +630,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>504825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -648,7 +648,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="6727825"/>
+          <a:off x="9848850" y="3114675"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDocument">
@@ -683,16 +683,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -701,7 +701,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4048125" y="7616825"/>
+          <a:off x="11315700" y="3400425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
@@ -736,16 +736,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -754,7 +754,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5648325" y="8505825"/>
+          <a:off x="12782550" y="4543425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -789,16 +789,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -807,7 +807,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5648325" y="9394825"/>
+          <a:off x="14249400" y="4543425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -842,16 +842,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -860,7 +860,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5648325" y="11172825"/>
+          <a:off x="15716250" y="4829175"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -895,16 +895,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>504825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -913,7 +913,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5648325" y="10283825"/>
+          <a:off x="15716250" y="4257675"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDocument">
@@ -948,16 +948,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -966,7 +966,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7248525" y="11172825"/>
+          <a:off x="17183100" y="5686425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1001,16 +1001,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1019,7 +1019,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7248525" y="12061825"/>
+          <a:off x="18649950" y="5686425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -1054,16 +1054,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1072,7 +1072,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7248525" y="15617825"/>
+          <a:off x="20116800" y="5972175"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1107,16 +1107,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>504825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1125,7 +1125,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7248525" y="12950825"/>
+          <a:off x="20116800" y="5400675"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1160,16 +1160,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1178,7 +1178,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7248525" y="13839825"/>
+          <a:off x="21583650" y="5686425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1213,16 +1213,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1231,7 +1231,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7248525" y="14728825"/>
+          <a:off x="23050500" y="5686425"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -1267,28 +1267,28 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="22" name="Edge_22"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="2"/>
-          <a:endCxn id="3" idx="0"/>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="3" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1466850" y="1831975"/>
-          <a:ext cx="1" cy="450850"/>
+          <a:off x="1047750" y="1114425"/>
+          <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1305,29 +1305,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="23" name="Edge_23"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="3" idx="2"/>
-          <a:endCxn id="6" idx="0"/>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1466850" y="2720975"/>
-          <a:ext cx="3200400" cy="1339850"/>
+          <a:off x="2514600" y="1114425"/>
+          <a:ext cx="2933700" cy="2286000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1344,16 +1344,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>711200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>882650</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>485775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>971550</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>657225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1362,7 +1362,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1228725" y="2768600"/>
+          <a:off x="4362450" y="2390775"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1395,29 +1395,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="25" name="Edge_25"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="3" idx="3"/>
-          <a:endCxn id="4" idx="0"/>
+          <a:endCxn id="4" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2085975" y="2501900"/>
-          <a:ext cx="981075" cy="669925"/>
+          <a:off x="2514600" y="1114425"/>
+          <a:ext cx="1466850" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1434,16 +1434,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>358775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>530225</xdr:rowOff>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1452,7 +1452,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1981200" y="2416175"/>
+          <a:off x="3629025" y="1819275"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1485,29 +1485,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="27" name="Edge_27"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="2"/>
-          <a:endCxn id="6" idx="0"/>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="6" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3067050" y="3609975"/>
-          <a:ext cx="1600200" cy="450850"/>
+          <a:off x="3981450" y="2257425"/>
+          <a:ext cx="1466850" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1524,16 +1524,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>711200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>882650</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1542,7 +1542,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2828925" y="3657600"/>
+          <a:off x="5095875" y="2962275"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1575,29 +1575,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="29" name="Edge_29"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="1"/>
-          <a:endCxn id="5" idx="0"/>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="5" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1466850" y="3390900"/>
-          <a:ext cx="981075" cy="669925"/>
+        <a:xfrm flipV="1">
+          <a:off x="3981450" y="1114425"/>
+          <a:ext cx="1466850" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1614,16 +1614,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1409700</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>358775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>530225</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1632,7 +1632,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2076450" y="3305175"/>
+          <a:off x="5095875" y="1819275"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1665,34 +1665,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="Back_31"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="31" name="Edge_31"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="3"/>
+          <a:endCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="4279900"/>
-          <a:ext cx="514350" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+        <a:xfrm flipH="1">
+          <a:off x="1047750" y="1114425"/>
+          <a:ext cx="4400550" cy="1"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -1700,34 +1704,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="Back_32"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="32" name="Edge_32"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="3"/>
+          <a:endCxn id="7" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="1612900"/>
-          <a:ext cx="0" cy="2667000"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="5448300" y="3400425"/>
+          <a:ext cx="1466850" cy="1"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -1735,28 +1743,31 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="Back_33"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="33" name="Edge_33"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="7" idx="3"/>
+          <a:endCxn id="8" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="1612900"/>
-          <a:ext cx="514350" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+          <a:off x="6915150" y="3400425"/>
+          <a:ext cx="1466850" cy="1"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="12700">
@@ -1771,29 +1782,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="34" name="Edge_34"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="6" idx="2"/>
-          <a:endCxn id="7" idx="0"/>
+          <a:stCxn id="8" idx="3"/>
+          <a:endCxn id="10" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4667250" y="4498975"/>
-          <a:ext cx="1" cy="450850"/>
+        <a:xfrm flipV="1">
+          <a:off x="8382000" y="3114675"/>
+          <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1810,103 +1821,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="35" name="Edge_35"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="7" idx="2"/>
-          <a:endCxn id="8" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4667250" y="5387975"/>
-          <a:ext cx="1" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="36" name="Edge_36"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="2"/>
-          <a:endCxn id="10" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4667250" y="6276975"/>
-          <a:ext cx="1" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>711200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>882650</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="Label_37"/>
+        <xdr:cNvPr id="35" name="Label_35"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4429125" y="6324600"/>
+          <a:off x="9496425" y="3390900"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1939,29 +1872,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Edge_38"/>
+        <xdr:cNvPr id="36" name="Edge_36"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="3"/>
-          <a:endCxn id="9" idx="0"/>
+          <a:endCxn id="9" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="4667250" y="6057900"/>
-          <a:ext cx="619125" cy="2447925"/>
+        <a:xfrm>
+          <a:off x="8382000" y="3400425"/>
+          <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1978,25 +1911,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>358775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>530225</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>800100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="Label_39"/>
+        <xdr:cNvPr id="37" name="Label_37"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5181600" y="5972175"/>
+          <a:off x="9496425" y="3676650"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2029,34 +1962,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="Back_40"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="38" name="Edge_38"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="3"/>
+          <a:endCxn id="7" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="8724900"/>
-          <a:ext cx="3714750" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6915150" y="3400425"/>
+          <a:ext cx="2933700" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2064,34 +2001,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="41" name="Back_41"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="39" name="Edge_39"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="11" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="5168900"/>
-          <a:ext cx="0" cy="3556000"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="9848850" y="3114675"/>
+          <a:ext cx="1466850" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2099,28 +2040,31 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="Back_42"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="40" name="Edge_40"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="11" idx="3"/>
+          <a:endCxn id="12" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="5168900"/>
-          <a:ext cx="3714750" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+          <a:off x="11315700" y="3400425"/>
+          <a:ext cx="1466850" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="12700">
@@ -2135,29 +2079,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="Edge_43"/>
+        <xdr:cNvPr id="41" name="Edge_41"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="10" idx="2"/>
-          <a:endCxn id="11" idx="0"/>
+          <a:stCxn id="12" idx="3"/>
+          <a:endCxn id="13" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4667250" y="7165975"/>
-          <a:ext cx="1" cy="450850"/>
+          <a:off x="12782550" y="4543425"/>
+          <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2174,29 +2118,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="Edge_44"/>
+        <xdr:cNvPr id="42" name="Edge_42"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="11" idx="2"/>
-          <a:endCxn id="12" idx="0"/>
+          <a:stCxn id="13" idx="3"/>
+          <a:endCxn id="15" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4667250" y="8054975"/>
-          <a:ext cx="1600200" cy="450850"/>
+        <a:xfrm flipV="1">
+          <a:off x="14249400" y="4257675"/>
+          <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2213,103 +2157,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="45" name="Edge_45"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="12" idx="2"/>
-          <a:endCxn id="13" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6267450" y="8943975"/>
-          <a:ext cx="1" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="Edge_46"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="13" idx="2"/>
-          <a:endCxn id="15" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6267450" y="9832975"/>
-          <a:ext cx="1" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>711200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>882650</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="Label_47"/>
+        <xdr:cNvPr id="43" name="Label_43"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6029325" y="9880600"/>
+          <a:off x="15363825" y="4533900"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2342,29 +2208,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Edge_48"/>
+        <xdr:cNvPr id="44" name="Edge_44"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="13" idx="3"/>
-          <a:endCxn id="14" idx="0"/>
+          <a:endCxn id="14" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="6267450" y="9613900"/>
-          <a:ext cx="619125" cy="1558925"/>
+        <a:xfrm>
+          <a:off x="14249400" y="4543425"/>
+          <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2381,25 +2247,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>358775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>530225</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>800100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="Label_49"/>
+        <xdr:cNvPr id="45" name="Label_45"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6781800" y="9528175"/>
+          <a:off x="15363825" y="4819650"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2432,34 +2298,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="50" name="Back_50"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="46" name="Edge_46"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+          <a:endCxn id="11" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="11391900"/>
-          <a:ext cx="5314950" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="11315700" y="3400425"/>
+          <a:ext cx="4400550" cy="1428750"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2467,34 +2337,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="51" name="Back_51"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="47" name="Edge_47"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+          <a:endCxn id="16" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="7835900"/>
-          <a:ext cx="0" cy="3556000"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="15716250" y="4257675"/>
+          <a:ext cx="1466850" cy="1428750"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2502,28 +2376,31 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Back_52"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="48" name="Edge_48"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="7835900"/>
-          <a:ext cx="3714750" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+          <a:off x="17183100" y="5686425"/>
+          <a:ext cx="1466850" cy="1"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="12700">
@@ -2538,29 +2415,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="53" name="Edge_53"/>
+        <xdr:cNvPr id="49" name="Edge_49"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="15" idx="2"/>
-          <a:endCxn id="16" idx="0"/>
+          <a:stCxn id="17" idx="3"/>
+          <a:endCxn id="19" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6267450" y="10721975"/>
-          <a:ext cx="1600200" cy="450850"/>
+        <a:xfrm flipV="1">
+          <a:off x="18649950" y="5400675"/>
+          <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2577,103 +2454,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="54" name="Edge_54"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="16" idx="2"/>
-          <a:endCxn id="17" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7867650" y="11610975"/>
-          <a:ext cx="1" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="Edge_55"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="2"/>
-          <a:endCxn id="19" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7867650" y="12499975"/>
-          <a:ext cx="1" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>711200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>882650</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="Label_56"/>
+        <xdr:cNvPr id="50" name="Label_50"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7629525" y="12547600"/>
+          <a:off x="19764375" y="5676900"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2706,29 +2505,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="57" name="Edge_57"/>
+        <xdr:cNvPr id="51" name="Edge_51"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="17" idx="3"/>
-          <a:endCxn id="18" idx="0"/>
+          <a:endCxn id="18" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7867650" y="12280900"/>
-          <a:ext cx="619125" cy="3336925"/>
+        <a:xfrm>
+          <a:off x="18649950" y="5686425"/>
+          <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2745,25 +2544,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>358775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1790700</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>530225</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>800100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="Label_58"/>
+        <xdr:cNvPr id="52" name="Label_52"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8382000" y="12195175"/>
+          <a:off x="19764375" y="5962650"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2796,34 +2595,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="59" name="Back_59"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="53" name="Edge_53"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="3"/>
+          <a:endCxn id="17" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="15836900"/>
-          <a:ext cx="6915150" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="18649950" y="5686425"/>
+          <a:ext cx="1466850" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2831,34 +2634,38 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="60" name="Back_60"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="54" name="Edge_54"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="19" idx="3"/>
+          <a:endCxn id="20" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="12280900"/>
-          <a:ext cx="0" cy="3556000"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="20116800" y="5400675"/>
+          <a:ext cx="1466850" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2866,104 +2673,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>444500</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="61" name="Back_61"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="333375" y="12280900"/>
-          <a:ext cx="6915150" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="62" name="Edge_62"/>
+        <xdr:cNvPr id="55" name="Edge_55"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="19" idx="2"/>
-          <a:endCxn id="20" idx="0"/>
+          <a:stCxn id="20" idx="3"/>
+          <a:endCxn id="21" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7867650" y="13388975"/>
-          <a:ext cx="1" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>663575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>225425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="63" name="Edge_63"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="20" idx="2"/>
-          <a:endCxn id="21" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7867650" y="14277975"/>
-          <a:ext cx="1" cy="450850"/>
+          <a:off x="21583650" y="5686425"/>
+          <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -3270,15 +3002,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3291,160 +3034,129 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>⚠ このシートは自動生成です。図形はドラッグ/リサイズ/テキスト編集できますが、再生成時に「フロー図」シートは上書きされます。手書きメモは「注記」シートに残してください。</t>
+          <t>⚠ このシートは自動生成です。図形はドラッグ/リサイズ/テキスト編集できますが、再生成時に「フロー図」シートは上書きされます。手書きメモは「注記」シートに残してください。 [layout warnings: cell-stacked: n8 and n9 share the same (lane, rank). / cell-stacked: n13 and n14 share the same (lane, rank). / cell-stacked: n17 and n18 share the same (lane, rank).]</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="3" t="inlineStr">
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>発注申請部</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>部長</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>購買部</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>倉庫</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="70" customHeight="1">
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="5" t="n"/>
+      <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="70" customHeight="1">
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="70" customHeight="1">
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/examples/purchase_process.xlsx
+++ b/examples/purchase_process.xlsx
@@ -10,7 +10,9 @@
     <sheet name="フロー図" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="注記" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'フロー図'!$A$1:$Q$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -208,13 +210,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -224,7 +226,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1047750" y="1114425"/>
+          <a:off x="1047750" y="1520825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -261,13 +263,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -277,7 +279,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="1114425"/>
+          <a:off x="2514600" y="1520825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -314,13 +316,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -330,7 +332,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3981450" y="2257425"/>
+          <a:off x="3981450" y="2663825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -367,13 +369,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -383,7 +385,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5448300" y="1114425"/>
+          <a:off x="5448300" y="1520825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -420,13 +422,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -436,7 +438,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5448300" y="3400425"/>
+          <a:off x="5448300" y="3806825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -473,13 +475,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -489,7 +491,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6915150" y="3400425"/>
+          <a:off x="6915150" y="3806825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -526,13 +528,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -542,7 +544,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8382000" y="3400425"/>
+          <a:off x="8382000" y="3806825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -579,13 +581,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>638175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -595,7 +597,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9848850" y="3686175"/>
+          <a:off x="9848850" y="4092575"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -632,13 +634,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>504825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -648,7 +650,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9848850" y="3114675"/>
+          <a:off x="9848850" y="3521075"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDocument">
@@ -685,13 +687,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -701,7 +703,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11315700" y="3400425"/>
+          <a:off x="11315700" y="3806825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
@@ -738,13 +740,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -754,7 +756,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12782550" y="4543425"/>
+          <a:off x="12782550" y="4949825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -791,13 +793,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -807,7 +809,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14249400" y="4543425"/>
+          <a:off x="14249400" y="4949825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -844,13 +846,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>638175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -860,7 +862,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15716250" y="4829175"/>
+          <a:off x="15716250" y="5235575"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -897,13 +899,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>504825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -913,7 +915,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15716250" y="4257675"/>
+          <a:off x="15716250" y="4664075"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDocument">
@@ -950,13 +952,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -966,7 +968,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17183100" y="5686425"/>
+          <a:off x="17183100" y="6092825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1003,13 +1005,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1019,7 +1021,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18649950" y="5686425"/>
+          <a:off x="18649950" y="6092825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -1056,13 +1058,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>638175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1072,7 +1074,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20116800" y="5972175"/>
+          <a:off x="20116800" y="6378575"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1109,13 +1111,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>504825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1125,7 +1127,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20116800" y="5400675"/>
+          <a:off x="20116800" y="5807075"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1162,13 +1164,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1178,7 +1180,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21583650" y="5686425"/>
+          <a:off x="21583650" y="6092825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -1215,13 +1217,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>790575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1231,7 +1233,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23050500" y="5686425"/>
+          <a:off x="23050500" y="6092825"/>
           <a:ext cx="1238250" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartTerminator">
@@ -1268,13 +1270,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1287,7 +1289,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1047750" y="1114425"/>
+          <a:off x="1047750" y="1520825"/>
           <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1307,13 +1309,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1326,7 +1328,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="1114425"/>
+          <a:off x="2514600" y="1520825"/>
           <a:ext cx="2933700" cy="2286000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1344,16 +1346,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>485775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>971550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1362,7 +1364,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4362450" y="2390775"/>
+          <a:off x="3848100" y="2225675"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1397,13 +1399,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1416,7 +1418,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="1114425"/>
+          <a:off x="2514600" y="1520825"/>
           <a:ext cx="1466850" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1435,15 +1437,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1057275</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>771525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>942975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1452,7 +1454,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3629025" y="1819275"/>
+          <a:off x="3848100" y="1939925"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1487,13 +1489,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1506,7 +1508,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3981450" y="2257425"/>
+          <a:off x="3981450" y="2663825"/>
           <a:ext cx="1466850" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1525,15 +1527,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1057275</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>771525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>942975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1542,7 +1544,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5095875" y="2962275"/>
+          <a:off x="5314950" y="3082925"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1577,13 +1579,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1596,7 +1598,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3981450" y="1114425"/>
+          <a:off x="3981450" y="1520825"/>
           <a:ext cx="1466850" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1615,15 +1617,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1057275</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>371475</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1632,7 +1634,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5095875" y="1819275"/>
+          <a:off x="5314950" y="2511425"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1667,27 +1669,27 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>390525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>352426</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="31" name="Edge_31"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="3"/>
-          <a:endCxn id="2" idx="1"/>
+          <a:stCxn id="5" idx="0"/>
+          <a:endCxn id="2" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1047750" y="1114425"/>
-          <a:ext cx="4400550" cy="1"/>
+          <a:off x="1047750" y="746125"/>
+          <a:ext cx="4400550" cy="993775"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1706,13 +1708,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1725,7 +1727,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5448300" y="3400425"/>
+          <a:off x="5448300" y="3806825"/>
           <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1745,13 +1747,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1764,7 +1766,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6915150" y="3400425"/>
+          <a:off x="6915150" y="3806825"/>
           <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1784,13 +1786,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1803,7 +1805,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="8382000" y="3114675"/>
+          <a:off x="8382000" y="3521075"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1822,15 +1824,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>414337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>514350</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>585787</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1839,7 +1841,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9496425" y="3390900"/>
+          <a:off x="9715500" y="3868737"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1874,13 +1876,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1893,7 +1895,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8382000" y="3400425"/>
+          <a:off x="8382000" y="3806825"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -1912,15 +1914,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>628650</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>557212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>800100</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>728662</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1929,7 +1931,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9496425" y="3676650"/>
+          <a:off x="9715500" y="4011612"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1964,27 +1966,27 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>390525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>857250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="38" name="Edge_38"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="9" idx="3"/>
-          <a:endCxn id="7" idx="1"/>
+          <a:stCxn id="9" idx="0"/>
+          <a:endCxn id="7" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="6915150" y="3400425"/>
-          <a:ext cx="2933700" cy="285750"/>
+          <a:off x="6915150" y="746125"/>
+          <a:ext cx="2933700" cy="3565525"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2003,13 +2005,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2022,7 +2024,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9848850" y="3114675"/>
+          <a:off x="9848850" y="3521075"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2042,13 +2044,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2061,7 +2063,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11315700" y="3400425"/>
+          <a:off x="11315700" y="3806825"/>
           <a:ext cx="1466850" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2081,13 +2083,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2100,7 +2102,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12782550" y="4543425"/>
+          <a:off x="12782550" y="4949825"/>
           <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2120,13 +2122,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2139,7 +2141,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="14249400" y="4257675"/>
+          <a:off x="14249400" y="4664075"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2158,15 +2160,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>414337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>514350</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>585787</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2175,7 +2177,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15363825" y="4533900"/>
+          <a:off x="15582900" y="5011737"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2210,13 +2212,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2229,7 +2231,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14249400" y="4543425"/>
+          <a:off x="14249400" y="4949825"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2248,15 +2250,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>628650</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>557212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>800100</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>728662</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2265,7 +2267,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15363825" y="4819650"/>
+          <a:off x="15582900" y="5154612"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2300,27 +2302,27 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>390525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>857250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="46" name="Edge_46"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="14" idx="3"/>
-          <a:endCxn id="11" idx="1"/>
+          <a:stCxn id="14" idx="0"/>
+          <a:endCxn id="11" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="11315700" y="3400425"/>
-          <a:ext cx="4400550" cy="1428750"/>
+          <a:off x="11315700" y="746125"/>
+          <a:ext cx="4400550" cy="4708525"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2339,13 +2341,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2358,7 +2360,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15716250" y="4257675"/>
+          <a:off x="15716250" y="4664075"/>
           <a:ext cx="1466850" cy="1428750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2378,13 +2380,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2397,7 +2399,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17183100" y="5686425"/>
+          <a:off x="17183100" y="6092825"/>
           <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2417,13 +2419,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2436,7 +2438,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="18649950" y="5400675"/>
+          <a:off x="18649950" y="5807075"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2455,15 +2457,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>414337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>514350</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>585787</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2472,7 +2474,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19764375" y="5676900"/>
+          <a:off x="19983450" y="6154737"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2507,13 +2509,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2526,7 +2528,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18649950" y="5686425"/>
+          <a:off x="18649950" y="6092825"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2545,15 +2547,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>628650</xdr:rowOff>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>557212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>800100</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>728662</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2562,7 +2564,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19764375" y="5962650"/>
+          <a:off x="19983450" y="6297612"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2597,27 +2599,27 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>390525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>857250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="53" name="Edge_53"/>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="18" idx="3"/>
-          <a:endCxn id="17" idx="1"/>
+          <a:stCxn id="18" idx="0"/>
+          <a:endCxn id="17" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="18649950" y="5686425"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="18649950" y="746125"/>
+          <a:ext cx="1466850" cy="5851525"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2636,13 +2638,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2655,7 +2657,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20116800" y="5400675"/>
+          <a:off x="20116800" y="5807075"/>
           <a:ext cx="1466850" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -2675,13 +2677,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>352426</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2694,7 +2696,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21583650" y="5686425"/>
+          <a:off x="21583650" y="6092825"/>
           <a:ext cx="1466850" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
@@ -3000,9 +3002,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3038,127 +3040,129 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="32" customHeight="1"/>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>発注申請部</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="n"/>
     </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>部長</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
     </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>購買部</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>倉庫</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
     </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/examples/purchase_process.xlsx
+++ b/examples/purchase_process.xlsx
@@ -1269,15 +1269,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>352426</xdr:rowOff>
+      <xdr:rowOff>571501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1289,8 +1289,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1047750" y="1520825"/>
-          <a:ext cx="1466850" cy="1"/>
+          <a:off x="2286000" y="1739900"/>
+          <a:ext cx="228600" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1308,15 +1308,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1328,8 +1328,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="1520825"/>
-          <a:ext cx="2933700" cy="2286000"/>
+          <a:off x="3752850" y="1739900"/>
+          <a:ext cx="1695450" cy="2286000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1398,15 +1398,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1418,8 +1418,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="1520825"/>
-          <a:ext cx="1466850" cy="1143000"/>
+          <a:off x="3752850" y="1739900"/>
+          <a:ext cx="228600" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1488,15 +1488,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1508,8 +1508,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3981450" y="2663825"/>
-          <a:ext cx="1466850" cy="1143000"/>
+          <a:off x="5219700" y="2882900"/>
+          <a:ext cx="228600" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1578,15 +1578,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1598,8 +1598,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3981450" y="1520825"/>
-          <a:ext cx="1466850" cy="1143000"/>
+          <a:off x="5219700" y="1739900"/>
+          <a:ext cx="228600" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1667,38 +1667,34 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
+      <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="Edge_31"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="0"/>
-          <a:endCxn id="2" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvPr id="31" name="Back_31"/>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1047750" y="746125"/>
-          <a:ext cx="4400550" cy="993775"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
+        <a:xfrm>
+          <a:off x="6067425" y="965200"/>
+          <a:ext cx="0" cy="555625"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -1706,20 +1702,91 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>352426</xdr:rowOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="Edge_32"/>
+        <xdr:cNvPr id="32" name="Back_32"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1666875" y="965200"/>
+          <a:ext cx="4400550" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="Back_33"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1666875" y="965200"/>
+          <a:ext cx="0" cy="555625"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>571501</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Edge_34"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="3"/>
           <a:endCxn id="7" idx="1"/>
@@ -1727,8 +1794,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5448300" y="3806825"/>
-          <a:ext cx="1466850" cy="1"/>
+          <a:off x="6686550" y="4025900"/>
+          <a:ext cx="228600" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1746,19 +1813,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>352426</xdr:rowOff>
+      <xdr:rowOff>571501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="Edge_33"/>
+        <xdr:cNvPr id="35" name="Edge_35"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="3"/>
           <a:endCxn id="8" idx="1"/>
@@ -1766,8 +1833,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6915150" y="3806825"/>
-          <a:ext cx="1466850" cy="1"/>
+          <a:off x="8153400" y="4025900"/>
+          <a:ext cx="228600" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1785,19 +1852,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>285750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="Edge_34"/>
+        <xdr:cNvPr id="36" name="Edge_36"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="3"/>
           <a:endCxn id="10" idx="1"/>
@@ -1805,8 +1872,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="8382000" y="3521075"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="9620250" y="3740150"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1836,7 +1903,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="Label_35"/>
+        <xdr:cNvPr id="37" name="Label_37"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1875,19 +1942,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
+      <xdr:rowOff>857250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="36" name="Edge_36"/>
+        <xdr:cNvPr id="38" name="Edge_38"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="3"/>
           <a:endCxn id="9" idx="1"/>
@@ -1895,8 +1962,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8382000" y="3806825"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="9620250" y="4025900"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1926,7 +1993,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="Label_37"/>
+        <xdr:cNvPr id="39" name="Label_39"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1964,38 +2031,34 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>857250</xdr:rowOff>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Edge_38"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="9" idx="0"/>
-          <a:endCxn id="7" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvPr id="40" name="Back_40"/>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="6915150" y="746125"/>
-          <a:ext cx="2933700" cy="3565525"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
+        <a:xfrm>
+          <a:off x="10467975" y="965200"/>
+          <a:ext cx="0" cy="3127375"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2003,20 +2066,91 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="41" name="Back_41"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7534275" y="965200"/>
+          <a:ext cx="2933700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="39" name="Edge_39"/>
+        <xdr:cNvPr id="42" name="Back_42"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7534275" y="965200"/>
+          <a:ext cx="0" cy="2841625"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="Edge_43"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="10" idx="3"/>
           <a:endCxn id="11" idx="1"/>
@@ -2024,8 +2158,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9848850" y="3521075"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="11087100" y="3740150"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2043,19 +2177,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="Edge_40"/>
+        <xdr:cNvPr id="44" name="Edge_44"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="11" idx="3"/>
           <a:endCxn id="12" idx="1"/>
@@ -2063,8 +2197,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11315700" y="3806825"/>
-          <a:ext cx="1466850" cy="1143000"/>
+          <a:off x="12553950" y="4025900"/>
+          <a:ext cx="228600" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2082,19 +2216,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>352426</xdr:rowOff>
+      <xdr:rowOff>571501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="41" name="Edge_41"/>
+        <xdr:cNvPr id="45" name="Edge_45"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="12" idx="3"/>
           <a:endCxn id="13" idx="1"/>
@@ -2102,8 +2236,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12782550" y="4949825"/>
-          <a:ext cx="1466850" cy="1"/>
+          <a:off x="14020800" y="5168900"/>
+          <a:ext cx="228600" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2121,19 +2255,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>285750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="Edge_42"/>
+        <xdr:cNvPr id="46" name="Edge_46"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="13" idx="3"/>
           <a:endCxn id="15" idx="1"/>
@@ -2141,8 +2275,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="14249400" y="4664075"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="15487650" y="4883150"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2172,7 +2306,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="Label_43"/>
+        <xdr:cNvPr id="47" name="Label_47"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2211,19 +2345,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
+      <xdr:rowOff>857250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="Edge_44"/>
+        <xdr:cNvPr id="48" name="Edge_48"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="13" idx="3"/>
           <a:endCxn id="14" idx="1"/>
@@ -2231,8 +2365,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14249400" y="4949825"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="15487650" y="5168900"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2262,7 +2396,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="Label_45"/>
+        <xdr:cNvPr id="49" name="Label_49"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2300,38 +2434,34 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>857250</xdr:rowOff>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="Edge_46"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="14" idx="0"/>
-          <a:endCxn id="11" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvPr id="50" name="Back_50"/>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="11315700" y="746125"/>
-          <a:ext cx="4400550" cy="4708525"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
+        <a:xfrm>
+          <a:off x="16335375" y="965200"/>
+          <a:ext cx="0" cy="4270375"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2339,20 +2469,91 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="Edge_47"/>
+        <xdr:cNvPr id="51" name="Back_51"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11934825" y="965200"/>
+          <a:ext cx="4400550" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="Back_52"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11934825" y="965200"/>
+          <a:ext cx="0" cy="2841625"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="53" name="Edge_53"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="15" idx="3"/>
           <a:endCxn id="16" idx="1"/>
@@ -2360,8 +2561,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15716250" y="4664075"/>
-          <a:ext cx="1466850" cy="1428750"/>
+          <a:off x="16954500" y="4883150"/>
+          <a:ext cx="228600" cy="1428750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2379,19 +2580,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>352426</xdr:rowOff>
+      <xdr:rowOff>571501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Edge_48"/>
+        <xdr:cNvPr id="54" name="Edge_54"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="16" idx="3"/>
           <a:endCxn id="17" idx="1"/>
@@ -2399,8 +2600,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17183100" y="6092825"/>
-          <a:ext cx="1466850" cy="1"/>
+          <a:off x="18421350" y="6311900"/>
+          <a:ext cx="228600" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2418,19 +2619,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>285750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="49" name="Edge_49"/>
+        <xdr:cNvPr id="55" name="Edge_55"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="17" idx="3"/>
           <a:endCxn id="19" idx="1"/>
@@ -2438,8 +2639,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="18649950" y="5807075"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="19888200" y="6026150"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2469,7 +2670,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="Label_50"/>
+        <xdr:cNvPr id="56" name="Label_56"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2508,19 +2709,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
+      <xdr:rowOff>857250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="51" name="Edge_51"/>
+        <xdr:cNvPr id="57" name="Edge_57"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="17" idx="3"/>
           <a:endCxn id="18" idx="1"/>
@@ -2528,8 +2729,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18649950" y="6092825"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="19888200" y="6311900"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2559,7 +2760,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="Label_52"/>
+        <xdr:cNvPr id="58" name="Label_58"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2597,38 +2798,34 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>857250</xdr:rowOff>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="53" name="Edge_53"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="18" idx="0"/>
-          <a:endCxn id="17" idx="0"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvPr id="59" name="Back_59"/>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="18649950" y="746125"/>
-          <a:ext cx="1466850" cy="5851525"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
+        <a:xfrm>
+          <a:off x="20735925" y="965200"/>
+          <a:ext cx="0" cy="5413375"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2636,20 +2833,91 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="60" name="Back_60"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19269075" y="965200"/>
+          <a:ext cx="1466850" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="54" name="Edge_54"/>
+        <xdr:cNvPr id="61" name="Back_61"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19269075" y="965200"/>
+          <a:ext cx="0" cy="5127625"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="62" name="Edge_62"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="19" idx="3"/>
           <a:endCxn id="20" idx="1"/>
@@ -2657,8 +2925,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20116800" y="5807075"/>
-          <a:ext cx="1466850" cy="285750"/>
+          <a:off x="21355050" y="6026150"/>
+          <a:ext cx="228600" cy="285750"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -2676,19 +2944,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1352550</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>352426</xdr:rowOff>
+      <xdr:rowOff>571501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="Edge_55"/>
+        <xdr:cNvPr id="63" name="Edge_63"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="3"/>
           <a:endCxn id="21" idx="1"/>
@@ -2696,8 +2964,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21583650" y="6092825"/>
-          <a:ext cx="1466850" cy="1"/>
+          <a:off x="22821900" y="6311900"/>
+          <a:ext cx="228600" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>

--- a/examples/purchase_process.xlsx
+++ b/examples/purchase_process.xlsx
@@ -1667,7 +1667,7 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>733425</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
@@ -1681,20 +1681,44 @@
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="31" name="Back_31"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="0"/>
+          <a:endCxn id="2" idx="0"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6067425" y="965200"/>
-          <a:ext cx="0" cy="555625"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="1666875" y="965200"/>
+          <a:ext cx="4400550" cy="555625"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="100000" y="100000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="100000" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="100000"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -1702,91 +1726,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>571501</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="Back_32"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1666875" y="965200"/>
-          <a:ext cx="4400550" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="Back_33"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1666875" y="965200"/>
-          <a:ext cx="0" cy="555625"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="Edge_34"/>
+        <xdr:cNvPr id="32" name="Edge_32"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="3"/>
           <a:endCxn id="7" idx="1"/>
@@ -1825,7 +1778,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="35" name="Edge_35"/>
+        <xdr:cNvPr id="33" name="Edge_33"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="7" idx="3"/>
           <a:endCxn id="8" idx="1"/>
@@ -1864,7 +1817,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="36" name="Edge_36"/>
+        <xdr:cNvPr id="34" name="Edge_34"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="3"/>
           <a:endCxn id="10" idx="1"/>
@@ -1903,7 +1856,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="Label_37"/>
+        <xdr:cNvPr id="35" name="Label_35"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1954,7 +1907,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Edge_38"/>
+        <xdr:cNvPr id="36" name="Edge_36"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="3"/>
           <a:endCxn id="9" idx="1"/>
@@ -1993,7 +1946,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="Label_39"/>
+        <xdr:cNvPr id="37" name="Label_37"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2031,7 +1984,7 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>733425</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
@@ -2044,21 +1997,45 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="Back_40"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="38" name="Back_38"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="9" idx="0"/>
+          <a:endCxn id="7" idx="0"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10467975" y="965200"/>
-          <a:ext cx="0" cy="3127375"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="7534275" y="965200"/>
+          <a:ext cx="2933700" cy="3127375"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="100000" y="100000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="100000" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="90862"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2066,91 +2043,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="41" name="Back_41"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7534275" y="965200"/>
-          <a:ext cx="2933700" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="Back_42"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7534275" y="965200"/>
-          <a:ext cx="0" cy="2841625"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="Edge_43"/>
+        <xdr:cNvPr id="39" name="Edge_39"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="10" idx="3"/>
           <a:endCxn id="11" idx="1"/>
@@ -2189,7 +2095,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="Edge_44"/>
+        <xdr:cNvPr id="40" name="Edge_40"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="11" idx="3"/>
           <a:endCxn id="12" idx="1"/>
@@ -2228,7 +2134,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="45" name="Edge_45"/>
+        <xdr:cNvPr id="41" name="Edge_41"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="12" idx="3"/>
           <a:endCxn id="13" idx="1"/>
@@ -2267,7 +2173,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="Edge_46"/>
+        <xdr:cNvPr id="42" name="Edge_42"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="13" idx="3"/>
           <a:endCxn id="15" idx="1"/>
@@ -2306,7 +2212,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="Label_47"/>
+        <xdr:cNvPr id="43" name="Label_43"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2357,7 +2263,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Edge_48"/>
+        <xdr:cNvPr id="44" name="Edge_44"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="13" idx="3"/>
           <a:endCxn id="14" idx="1"/>
@@ -2396,7 +2302,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="Label_49"/>
+        <xdr:cNvPr id="45" name="Label_45"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2434,7 +2340,7 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>733425</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
@@ -2447,21 +2353,45 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="50" name="Back_50"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="46" name="Back_46"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="0"/>
+          <a:endCxn id="11" idx="0"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16335375" y="965200"/>
-          <a:ext cx="0" cy="4270375"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="11934825" y="965200"/>
+          <a:ext cx="4400550" cy="4270375"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="100000" y="100000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="100000" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="66542"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2469,91 +2399,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="51" name="Back_51"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11934825" y="965200"/>
-          <a:ext cx="4400550" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Back_52"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11934825" y="965200"/>
-          <a:ext cx="0" cy="2841625"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="53" name="Edge_53"/>
+        <xdr:cNvPr id="47" name="Edge_47"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="15" idx="3"/>
           <a:endCxn id="16" idx="1"/>
@@ -2592,7 +2451,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="54" name="Edge_54"/>
+        <xdr:cNvPr id="48" name="Edge_48"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="16" idx="3"/>
           <a:endCxn id="17" idx="1"/>
@@ -2631,7 +2490,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="Edge_55"/>
+        <xdr:cNvPr id="49" name="Edge_49"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="17" idx="3"/>
           <a:endCxn id="19" idx="1"/>
@@ -2670,7 +2529,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="Label_56"/>
+        <xdr:cNvPr id="50" name="Label_50"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2721,7 +2580,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="57" name="Edge_57"/>
+        <xdr:cNvPr id="51" name="Edge_51"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="17" idx="3"/>
           <a:endCxn id="18" idx="1"/>
@@ -2760,7 +2619,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="Label_58"/>
+        <xdr:cNvPr id="52" name="Label_52"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2798,7 +2657,7 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>733425</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>203200</xdr:rowOff>
@@ -2811,21 +2670,45 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="59" name="Back_59"/>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvPr id="53" name="Back_53"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="18" idx="0"/>
+          <a:endCxn id="17" idx="0"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20735925" y="965200"/>
-          <a:ext cx="0" cy="5413375"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
+          <a:off x="19269075" y="965200"/>
+          <a:ext cx="1466850" cy="5413375"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="100000" y="100000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="100000" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="94721"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
     </xdr:cxnSp>
@@ -2833,91 +2716,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="60" name="Back_60"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19269075" y="965200"/>
-          <a:ext cx="1466850" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="61" name="Back_61"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19269075" y="965200"/>
-          <a:ext cx="0" cy="5127625"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="62" name="Edge_62"/>
+        <xdr:cNvPr id="54" name="Edge_54"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="19" idx="3"/>
           <a:endCxn id="20" idx="1"/>
@@ -2956,7 +2768,7 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="63" name="Edge_63"/>
+        <xdr:cNvPr id="55" name="Edge_55"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="20" idx="3"/>
           <a:endCxn id="21" idx="1"/>

--- a/examples/purchase_process.xlsx
+++ b/examples/purchase_process.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="フロー図" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="注記" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フロー図" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="注記" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'フロー図'!$A$1:$Q$8</definedName>
@@ -209,6 +209,1314 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Edge_22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2228850" y="1682750"/>
+          <a:ext cx="342900" cy="114300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="50000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="83333" y="50000"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Edge_23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3695700" y="1682750"/>
+          <a:ext cx="1809750" cy="2400300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="3157" y="2380"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="2380"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="97619"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="96842" y="97619"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Edge_25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3695700" y="1682750"/>
+          <a:ext cx="342900" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="4545"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="4545"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="95454"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="95454"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Edge_27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5162550" y="2825750"/>
+          <a:ext cx="342900" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="4545"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="4545"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="95454"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="95454"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Edge_29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5162550" y="1682750"/>
+          <a:ext cx="342900" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="95454"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="95454"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="4545"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="4545"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1409700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1019175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Edge_31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1609725" y="1682750"/>
+          <a:ext cx="5133975" cy="504825"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="98886" y="11320"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="98886" y="88679"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="1113" y="88679"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="1113" y="54716"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Edge_32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6629400" y="3968750"/>
+          <a:ext cx="342900" cy="114300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="50000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="83333" y="50000"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Edge_33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8096250" y="3968750"/>
+          <a:ext cx="342900" cy="114300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="50000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="83333" y="50000"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Edge_34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9563100" y="3683000"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="85714"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="14285"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>914400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Edge_36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9563100" y="3968750"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="14285"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="85714"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>733425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1409700</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1085850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Edge_38"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7477125" y="4187825"/>
+          <a:ext cx="3667125" cy="352425"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="98441" y="35135"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="98441" y="83783"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="1558" y="83783"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="1558" y="16216"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Edge_39"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11029950" y="3683000"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="14285"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="85714"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Edge_40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12496800" y="3968750"/>
+          <a:ext cx="342900" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="4545"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="4545"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="95454"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="95454"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Edge_41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13963650" y="5111750"/>
+          <a:ext cx="342900" cy="114300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="50000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="83333" y="50000"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Edge_42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15430500" y="4826000"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="85714"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="14285"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>914400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Edge_44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15430500" y="5111750"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="14285"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="85714"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>733425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>790575</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>695325</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Edge_46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11877675" y="4187825"/>
+          <a:ext cx="4514850" cy="1104900"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="98734" y="94827"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="98734" y="50000"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="1265" y="50000"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="1265" y="5172"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Edge_47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16897350" y="4826000"/>
+          <a:ext cx="342900" cy="1543050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="3703"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="3703"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="96296"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="96296"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Edge_48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18364200" y="6254750"/>
+          <a:ext cx="342900" cy="114300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="50000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="83333" y="50000"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Edge_49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19831050" y="5969000"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="85714"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="14285"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>914400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Edge_51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19831050" y="6254750"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="14285"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="85714"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>733425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1409700</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1085850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Edge_53"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19211925" y="6473825"/>
+          <a:ext cx="2200275" cy="352425"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="97402" y="35135"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="97402" y="83783"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2597" y="83783"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2597" y="16216"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Edge_54"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21297900" y="5969000"/>
+          <a:ext cx="342900" cy="400050"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="14285"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="50000" y="14285"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="50000" y="85714"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="83333" y="85714"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1295400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>628650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="Edge_55"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22764750" y="6254750"/>
+          <a:ext cx="342900" cy="114300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="100000" b="100000"/>
+          <a:pathLst>
+            <a:path w="100000" h="100000">
+              <a:moveTo>
+                <a:pt x="16666" y="50000"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="83333" y="50000"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="333333"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>352425</xdr:rowOff>
@@ -1268,93 +2576,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>571501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="Edge_22"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="3"/>
-          <a:endCxn id="3" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2286000" y="1739900"/>
-          <a:ext cx="228600" cy="1"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="Edge_23"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="3" idx="3"/>
-          <a:endCxn id="6" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3752850" y="1739900"/>
-          <a:ext cx="1695450" cy="2286000"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1447800</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1364,7 +2594,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3848100" y="2225675"/>
+          <a:off x="3848100" y="3368675"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1398,54 +2628,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="25" name="Edge_25"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="3" idx="3"/>
-          <a:endCxn id="4" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3752850" y="1739900"/>
-          <a:ext cx="228600" cy="1143000"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1447800</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>771525</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>942975</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>371475</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1454,7 +2645,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3848100" y="1939925"/>
+          <a:off x="3848100" y="2511425"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1488,54 +2679,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="Edge_27"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="3"/>
-          <a:endCxn id="6" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5219700" y="2882900"/>
-          <a:ext cx="228600" cy="1143000"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1447800</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>771525</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>942975</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>371475</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1544,7 +2696,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5314950" y="3082925"/>
+          <a:off x="5314950" y="3654425"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1578,54 +2730,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="29" name="Edge_29"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="3"/>
-          <a:endCxn id="5" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5219700" y="1739900"/>
-          <a:ext cx="228600" cy="1143000"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1447800</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:rowOff>771525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>371475</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>942975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1634,7 +2747,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5314950" y="2511425"/>
+          <a:off x="5314950" y="1939925"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1667,192 +2780,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="Back_31"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="5" idx="0"/>
-          <a:endCxn id="2" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1666875" y="965200"/>
-          <a:ext cx="4400550" cy="555625"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="100000" b="100000"/>
-          <a:pathLst>
-            <a:path w="100000" h="100000">
-              <a:moveTo>
-                <a:pt x="100000" y="100000"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="100000" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="100000"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="Edge_32"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="6" idx="3"/>
-          <a:endCxn id="7" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6686550" y="4025900"/>
-          <a:ext cx="228600" cy="1"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="Edge_33"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="7" idx="3"/>
-          <a:endCxn id="8" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8153400" y="4025900"/>
-          <a:ext cx="228600" cy="1"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="Edge_34"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="3"/>
-          <a:endCxn id="10" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="9620250" y="3740150"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>414337</xdr:rowOff>
+      <xdr:rowOff>271462</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>585787</xdr:rowOff>
+      <xdr:rowOff>442912</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1861,7 +2798,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9715500" y="3868737"/>
+          <a:off x="9715500" y="3725862"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1895,54 +2832,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>857250</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="36" name="Edge_36"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="3"/>
-          <a:endCxn id="9" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9620250" y="4025900"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
       <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>557212</xdr:rowOff>
+      <xdr:rowOff>700087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>728662</xdr:rowOff>
+      <xdr:rowOff>871537</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1951,7 +2849,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9715500" y="4011612"/>
+          <a:off x="9715500" y="4154487"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1984,231 +2882,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Back_38"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="9" idx="0"/>
-          <a:endCxn id="7" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7534275" y="965200"/>
-          <a:ext cx="2933700" cy="3127375"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="100000" b="100000"/>
-          <a:pathLst>
-            <a:path w="100000" h="100000">
-              <a:moveTo>
-                <a:pt x="100000" y="100000"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="100000" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="90862"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="39" name="Edge_39"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="10" idx="3"/>
-          <a:endCxn id="11" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11087100" y="3740150"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="Edge_40"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="11" idx="3"/>
-          <a:endCxn id="12" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12553950" y="4025900"/>
-          <a:ext cx="228600" cy="1143000"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>571501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="41" name="Edge_41"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="12" idx="3"/>
-          <a:endCxn id="13" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14020800" y="5168900"/>
-          <a:ext cx="228600" cy="1"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="Edge_42"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="13" idx="3"/>
-          <a:endCxn id="15" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="15487650" y="4883150"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>414337</xdr:rowOff>
+      <xdr:rowOff>271462</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>585787</xdr:rowOff>
+      <xdr:rowOff>442912</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2217,7 +2900,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15582900" y="5011737"/>
+          <a:off x="15582900" y="4868862"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2251,54 +2934,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>857250</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="Edge_44"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="13" idx="3"/>
-          <a:endCxn id="14" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15487650" y="5168900"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
       <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>557212</xdr:rowOff>
+      <xdr:rowOff>700087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>728662</xdr:rowOff>
+      <xdr:rowOff>871537</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2307,7 +2951,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15582900" y="5154612"/>
+          <a:off x="15582900" y="5297487"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2340,192 +2984,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="Back_46"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="14" idx="0"/>
-          <a:endCxn id="11" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11934825" y="965200"/>
-          <a:ext cx="4400550" cy="4270375"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="100000" b="100000"/>
-          <a:pathLst>
-            <a:path w="100000" h="100000">
-              <a:moveTo>
-                <a:pt x="100000" y="100000"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="100000" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="66542"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="Edge_47"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="15" idx="3"/>
-          <a:endCxn id="16" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16954500" y="4883150"/>
-          <a:ext cx="228600" cy="1428750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Edge_48"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="16" idx="3"/>
-          <a:endCxn id="17" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18421350" y="6311900"/>
-          <a:ext cx="228600" cy="1"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="49" name="Edge_49"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="3"/>
-          <a:endCxn id="19" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="19888200" y="6026150"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>414337</xdr:rowOff>
+      <xdr:rowOff>271462</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>585787</xdr:rowOff>
+      <xdr:rowOff>442912</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2534,7 +3002,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19983450" y="6154737"/>
+          <a:off x="19983450" y="6011862"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2568,54 +3036,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>857250</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="51" name="Edge_51"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="17" idx="3"/>
-          <a:endCxn id="18" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19888200" y="6311900"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
       <xdr:colOff>1447800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>557212</xdr:rowOff>
+      <xdr:rowOff>700087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>728662</xdr:rowOff>
+      <xdr:rowOff>871537</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2624,7 +3053,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19983450" y="6297612"/>
+          <a:off x="19983450" y="6440487"/>
           <a:ext cx="476250" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2653,143 +3082,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="53" name="Back_53"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="18" idx="0"/>
-          <a:endCxn id="17" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19269075" y="965200"/>
-          <a:ext cx="1466850" cy="5413375"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="100000" b="100000"/>
-          <a:pathLst>
-            <a:path w="100000" h="100000">
-              <a:moveTo>
-                <a:pt x="100000" y="100000"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="100000" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="94721"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="54" name="Edge_54"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="19" idx="3"/>
-          <a:endCxn id="20" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="21355050" y="6026150"/>
-          <a:ext cx="228600" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>571501</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="Edge_55"/>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="20" idx="3"/>
-          <a:endCxn id="21" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="22821900" y="6311900"/>
-          <a:ext cx="228600" cy="1"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="333333"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
